--- a/astro-site/public/dl/haccp-templates/18-parasite-destruction-log.xlsx
+++ b/astro-site/public/dl/haccp-templates/18-parasite-destruction-log.xlsx
@@ -21,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy h:mm AM/PM"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="m/d/yy h:mm AM/PM"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -152,7 +153,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
@@ -162,7 +165,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -628,7 +631,7 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>▸ The "Status" says OK at -4 °F or below for the hours set in cell B3 (168 by default) or more, or at -31 °F or below for 15 hours or more. Any other combination is ALERT and the fish cannot be served raw.</t>
+          <t>▸ The "Status" says OK at -4 °F or below for the hours set in cell B3 (168 by default) or more, or at -31 °F or below for 15 hours or more; any other combination is ALERT. The Food Code also allows -31 °F (-35 °C) until solid and then -4 °F (-20 °C) for 24 hours: the Status does not check that route, so note it in "Notes" and verify it yourself before serving the fish raw.</t>
         </is>
       </c>
     </row>
@@ -670,14 +673,14 @@
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>▸ Fish cooked to 145 °F or above in the center (record it in template 16 (Cooking &amp; Reheating Temperature Log)).</t>
+          <t>▸ Fish cooked to 145 °F or above in the center: record it in template 16 (Cooking &amp; Reheating Temperature Log).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>▸ Aquaculture fish raised from embryos and fed only a diet that cannot contain viable parasites, as long as the producer states it IN WRITING: keep that supplier statement, it is what the inspector asks for. Molluscan shellfish and certain tuna species are also exempt (§3-402.11(B)).</t>
+          <t>▸ Exempt under §3-402.11(B): molluscan shellfish; certain tuna species (such as yellowfin, bigeye and albacore); scallop products that are the shucked adductor muscle only; fish roe removed from the skein and rinsed; and fish raised in net-pens or in land-based operations such as ponds or tanks and fed formulated feed that contains no live parasites. For farmed fish, keep the supplier's written statement on file (§3-402.12(C)): it is what the inspector asks for.</t>
         </is>
       </c>
     </row>
@@ -780,7 +783,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Minimum hours at -4 °F or below:</t>
@@ -1671,21 +1674,21 @@
     <row r="46" ht="12.2" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>Legal basis: FDA Food Code 2022 §3-402.11(A); records §3-402.12 (keep 90 days). The treatment must reach -4 °F or below for at least the hours set in cell B3 (168 by default) in ALL parts of the item, or -31 °F or below for at least 15 hours. UK/EU: 24 hours at -4 °F (-20 °C): type 24 in B3.</t>
+          <t>Legal basis: FDA Food Code 2022 §3-402.11(A); records §3-402.12 (keep 90 days). The treatment must reach -4 °F or below for at least the hours set in cell B3 (168 by default) in ALL parts of the item, or -31 °F or below for at least 15 hours, or -31 °F (-35 °C) until solid and then -4 °F (-20 °C) for 24 hours. The Status does not check this third route: note it in "Notes". UK/EU: 24 hours at -4 °F (-20 °C): type 24 in B3.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="12.2" customHeight="1">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>A household freezer does not reliably reach -4 °F under load: measure the temperature of the unit every time and enter it, because it is the column the inspector cross-checks against this log and against template 01 (Food Temperature Log: Coolers, Freezers &amp; Hot Holding).</t>
+          <t>A household freezer does not reliably reach -4 °F under load: measure the temperature of the unit every time and enter it, because it is the column the inspector cross-checks against this log and against template 01 (Food Temperature Log).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="24.5" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>Applies to marinated anchovies, ceviche, tartare, sashimi, sushi, marinated fish, lightly cooked pickled fish, light cures and herring. NOT required for fish cooked to the §3-401.11 temperature (145 °F in the center), for aquaculture fish that meets the exemption with the producer's written statement, or for molluscan shellfish.</t>
+          <t>Applies to marinated anchovies, ceviche, tartare, sashimi, sushi, marinated fish, lightly cooked pickled fish, light cures and herring. NOT required for fish cooked to the §3-401.11 temperature (145 °F in the center). Exempt under §3-402.11(B): molluscan shellfish, certain tuna species, scallop adductor muscle only, rinsed fish roe, and fish raised in net-pens or land-based operations on formulated feed, with a written supplier statement kept on file (§3-402.12(C)).</t>
         </is>
       </c>
     </row>
